--- a/docs/collections/cpas-takagi/metadata/data.xlsx
+++ b/docs/collections/cpas-takagi/metadata/data.xlsx
@@ -11414,7 +11414,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5c3ba777-7a6f-7e38-9dbd-62265dae2333/manifest</t>
   </si>
   <si>
-    <t>Harvard 1919-1920, History 17a. Prof. F. G. Turner</t>
+    <t>Harvard 1919-1920, History 17a. Prof. F. J. Turner</t>
   </si>
   <si>
     <t>870</t>
